--- a/duplicate_detection/data/spare_parts_screws.xlsx
+++ b/duplicate_detection/data/spare_parts_screws.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:F219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,10 +429,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Description (English)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description (Finnish)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>specification</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
@@ -451,10 +461,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>M8X30 8.8 ZINC</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>DIN 931</t>
         </is>
@@ -473,10 +493,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>M8 X 30 8.8 ZINC PLATED</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>DIN 931</t>
         </is>
@@ -495,10 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>M8X30 8.8 ZN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>DIN 931</t>
         </is>
@@ -517,10 +557,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>M10X50 10.9</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>DIN 912</t>
         </is>
@@ -539,10 +589,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>M10 X 50 10.9</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>DIN 912</t>
         </is>
@@ -561,10 +621,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>M12X60 8.8 FULL THREAD</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>ISO 4014</t>
         </is>
@@ -583,10 +653,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>M12 X 60 8.8 FULL THREAD</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>ISO 4014</t>
         </is>
@@ -605,10 +685,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>M16X80 8.8</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>ISO 4762</t>
         </is>
@@ -627,10 +717,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>M16 X 80 8.8</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>ISO 4762</t>
         </is>
@@ -649,10 +749,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>M20X90 8.8 HDG</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -671,10 +781,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>M20 X 90 8.8 HOT DIP GALVANIZED</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -683,42 +803,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCR-2012</t>
+          <t>SCR-2051</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HEX SCREW M10X40</t>
+          <t>HEX SCREW M6X20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M10X40 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M6X20 8.8</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCR-2013</t>
+          <t>SCR-2052</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HEX SCREW M10X40</t>
+          <t>HEXAGON SCREW M6X20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M10X40 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M6 X 20 8.8</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -727,174 +867,254 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCR-2014</t>
+          <t>SCR-2053</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HEX SCREW M12X50</t>
+          <t>HEX SCREW M10X30 A2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M12X50 10.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>M10X30 A2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ISO 4017</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCR-2015</t>
+          <t>SCR-2054</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEXAGON SCREW M12X50</t>
+          <t>HEXAGON SCREW M10X30 SS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M12 X 50 10.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M10 X 30 A2 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ISO 4017</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCR-2016</t>
+          <t>SCR-2055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HEX SCREW M4X10</t>
+          <t>SOCKET HEAD SCREW M12X40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M4X10 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M12X40 10.9</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCR-2017</t>
+          <t>SCR-2056</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HEX SCREW M4X16</t>
+          <t>HEX SOCKET SCREW M12X40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M4X16 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>M12 X 40 10.9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCR-2018</t>
+          <t>SCR-2057</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HEX SCREW M5X20</t>
+          <t>HEX SCREW M16X60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M5X20 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M16X60 8.8</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCR-2019</t>
+          <t>SCR-2058</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HEX SCREW M5X25</t>
+          <t>HEXAGON SCREW M16X60</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M5X25 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M16 X 60 8.8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCR-2020</t>
+          <t>SCR-2059</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HEX SCREW M6X16</t>
+          <t>HEX SCREW M24X100</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M6X16 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>M24X100 8.8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCR-2021</t>
+          <t>SCR-2060</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HEX SCREW M6X25</t>
+          <t>HEXAGON SCREW M24X100</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M6X25 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>M24 X 100 8.8</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>ISO 4014</t>
         </is>
@@ -903,42 +1123,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCR-2022</t>
+          <t>SCR-2061</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HEX SCREW M6X30</t>
+          <t>SOCKET HEAD SCREW M8X16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M6X30 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M8X16 10.9</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCR-2023</t>
+          <t>SCR-2062</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SOCKET HEAD SCREW M6X16</t>
+          <t>HEX SOCKET SCREW M8X16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M6X16 10.9</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>M8 X 16 10.9</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>DIN 912</t>
         </is>
@@ -947,20 +1187,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCR-2024</t>
+          <t>SCR-2063</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HEX SCREW M8X16</t>
+          <t>HEX SCREW M5X16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M8X16 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>M5X16 8.8</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -969,20 +1219,30 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCR-2025</t>
+          <t>SCR-2064</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HEX SCREW M8X20</t>
+          <t>HEXAGON SCREW M5X16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M8X20 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>M5 X 16 8.8</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -991,174 +1251,254 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCR-2026</t>
+          <t>SCR-2065</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HEX SCREW M8X40</t>
+          <t>HEX SCREW M20X60 HDG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M8X40 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>M20X60 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCR-2027</t>
+          <t>SCR-2066</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HEX SCREW M8X60</t>
+          <t>HEXAGON SCREW M20X60 HDG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M8X60 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>M20 X 60 8.8 HOT DIP GALVANIZED</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCR-2028</t>
+          <t>SCR-2067</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SOCKET HEAD SCREW M8X25</t>
+          <t>HEX SCREW M20X60 GALV</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M8X25 10.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DIN 912</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>M20X60 8.8 HDG COATED</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCR-2029</t>
+          <t>SCR-2068</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HEX SCREW M10X30</t>
+          <t>SOCKET HEAD SCREW M6X12 A4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M10X30 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>M6X12 A4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCR-2030</t>
+          <t>SCR-2069</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HEX SCREW M10X60</t>
+          <t>HEX SOCKET SCREW M6X12 SS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M10X60 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>M6 X 12 A4 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCR-2031</t>
+          <t>SCR-2070</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HEX SCREW M10X70</t>
+          <t>HEX SCREW M30X120</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M10X70 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>M30X120 8.8</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCR-2032</t>
+          <t>SCR-2071</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SOCKET HEAD SCREW M10X40</t>
+          <t>HEXAGON SCREW M30X120</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M10X40 12.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DIN 912</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>M30 X 120 8.8</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCR-2033</t>
+          <t>SCR-2151</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HEX SCREW M12X40</t>
+          <t>HEX SCREW M4X12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M12X40 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>M4X12 8.8</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -1167,42 +1507,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCR-2034</t>
+          <t>SCR-2152</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HEX SCREW M12X80</t>
+          <t>HEXAGON SCREW M4X12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M12X80 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>M4 X 12 8.8</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCR-2035</t>
+          <t>SCR-2153</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HEX SCREW M12X100</t>
+          <t>HEX SCREW M14X70</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M12X100 10.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>M14X70 8.8</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>ISO 4014</t>
         </is>
@@ -1211,108 +1571,158 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCR-2036</t>
+          <t>SCR-2154</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SOCKET HEAD SCREW M12X35</t>
+          <t>HEXAGON SCREW M14X70</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M12X35 10.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIN 912</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>M14 X 70 8.8</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCR-2037</t>
+          <t>SCR-2155</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HEX SCREW M14X60</t>
+          <t>SOCKET HEAD SCREW M8X50 A2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M14X60 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>M8X50 A2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCR-2038</t>
+          <t>SCR-2156</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HEX SCREW M16X60</t>
+          <t>HEX SOCKET SCREW M8X50 SS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>M16X60 8.8</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>M8 X 50 A2 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCR-2039</t>
+          <t>SCR-2157</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HEX SCREW M16X100</t>
+          <t>HEX SCREW M10X25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>M16X100 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>M10X25 8.8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCR-2040</t>
+          <t>SCR-2158</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HEX SCREW M16X120 HDG</t>
+          <t>HEXAGON SCREW M10X25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>M16X120 8.8 HDG</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>M10 X 25 8.8</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>DIN 933</t>
         </is>
@@ -1321,42 +1731,62 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCR-2041</t>
+          <t>SCR-2159</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEX SCREW M20X60</t>
+          <t>HEX SCREW M12X90</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M20X60 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>M12X90 8.8</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCR-2042</t>
+          <t>SCR-2160</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HEX SCREW M20X120 HDG</t>
+          <t>HEXAGON SCREW M12X90</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M20X120 8.8 HDG</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>M12 X 90 8.8</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>DIN 931</t>
         </is>
@@ -1365,86 +1795,126 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCR-2043</t>
+          <t>SCR-2012</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HEX SCREW M24X80</t>
+          <t>HEX SCREW M10X40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M24X80 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ISO 4014</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>M10X40 8.8</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCR-2044</t>
+          <t>SCR-2013</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HEX SCREW M24X100</t>
+          <t>HEX SCREW M10X40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>M24X100 10.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIN 931</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>M10X40 8.8</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCR-2045</t>
+          <t>SCR-2014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HEX SCREW M24X120 HDG</t>
+          <t>HEX SCREW M12X50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>M24X120 8.8 HDG</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DIN 933</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>M12X50 10.9</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCR-2046</t>
+          <t>SCR-2015</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEX SCREW M30X100</t>
+          <t>HEXAGON SCREW M12X50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M30X100 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>M12 X 50 10.9</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>ISO 4014</t>
         </is>
@@ -1453,20 +1923,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCR-2047</t>
+          <t>SCR-2072</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEX SCREW M30X120</t>
+          <t>HEX SCREW M16X70</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M30X120 8.8</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>M16X70 8.8</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>DIN 931</t>
         </is>
@@ -1475,42 +1955,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCR-2048</t>
+          <t>SCR-2073</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SOCKET HEAD SCREW M16X50</t>
+          <t>HEXAGON SCREW M16X70</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>M16X50 12.9</t>
+          <t>Hexagon screw</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DIN 912</t>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>M16X70 8.8</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCR-2049</t>
+          <t>SCR-2074</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SOCKET HEAD SCREW M20X60</t>
+          <t>SOCKET HEAD SCREW M8X30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>M20X60 10.9</t>
+          <t>Hexagon socket head screw</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>M8X30 12.9</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>DIN 912</t>
         </is>
@@ -1519,22 +2019,5408 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>SCR-2075</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HEX SOCKET SCREW M8X30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>M8X30 12.9</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SCR-2016</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>M4X10 8.8</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SCR-2017</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X16</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>M4X16 8.8</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SCR-2018</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X20</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>M5X20 8.8</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SCR-2019</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>M5X25 8.8</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SCR-2020</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X16</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>M6X16 8.8</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SCR-2021</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>M6X25 8.8</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SCR-2022</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>M6X30 8.8</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SCR-2023</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M6X16</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>M6X16 10.9</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SCR-2024</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>M8X16 8.8</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SCR-2025</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X20</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>M8X20 8.8</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SCR-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X40</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>M8X40 8.8</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SCR-2027</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X60</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>M8X60 8.8</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SCR-2028</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M8X25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>M8X25 10.9</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SCR-2029</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>M10X30 8.8</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SCR-2030</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X60</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>M10X60 8.8</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SCR-2031</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X70</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>M10X70 8.8</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SCR-2032</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X40</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>M10X40 12.9</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SCR-2033</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X40</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>M12X40 8.8</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SCR-2034</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X80</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>M12X80 8.8</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SCR-2035</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X100</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>M12X100 10.9</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SCR-2036</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X35</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>M12X35 10.9</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SCR-2037</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HEX SCREW M14X60</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>M14X60 8.8</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SCR-2038</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HEX SCREW M16X60</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>M16X60 8.8</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SCR-2039</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HEX SCREW M16X100</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>M16X100 8.8</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SCR-2040</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HEX SCREW M16X120 HDG</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>M16X120 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SCR-2041</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HEX SCREW M20X60</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>M20X60 8.8</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SCR-2042</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HEX SCREW M20X120 HDG</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>M20X120 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SCR-2043</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>HEX SCREW M24X80</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>M24X80 8.8</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SCR-2044</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HEX SCREW M24X100</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>M24X100 10.9</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SCR-2045</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HEX SCREW M24X120 HDG</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>M24X120 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SCR-2046</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HEX SCREW M30X100</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>M30X100 8.8</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SCR-2047</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HEX SCREW M30X120</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>M30X120 8.8</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SCR-2048</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M16X50</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>M16X50 12.9</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SCR-2049</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M20X60</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>M20X60 10.9</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>SCR-2050</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>SET SCREW M8X20</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>M8X20 45H</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SCR-2076</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SET SCREW M6X10</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>M6X10 45H</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SCR-2077</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SET SCREW M8X12</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>M8X12 45H</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SCR-2078</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SET SCREW M10X16</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>M10X16 45H</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SCR-2079</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GRUB SCREW M6X8</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Set screw, cup point</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, kupupää</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>M6X8 45H</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SCR-2080</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GRUB SCREW M8X10</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Set screw, cup point</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, kupupää</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>M8X10 45H</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SCR-2081</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M6X20</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>M6X20 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ISO 10642</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SCR-2082</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M8X25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>M8X25 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ISO 10642</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SCR-2083</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M10X30</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>M10X30 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>DIN 7991</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SCR-2084</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M12X40</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>M12X40 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DIN 7991</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SCR-2085</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M5X16</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>M5X16 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SCR-2086</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M6X20</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>M6X20 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SCR-2087</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M8X25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>M8X25 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SCR-2088</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M8X20</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>M8X20 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SCR-2089</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M10X25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>M10X25 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SCR-2090</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M12X30</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>M12X30 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SCR-2091</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X20 A2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>M4X20 A2 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ISO 4017</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SCR-2092</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X30 A2</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>M5X30 A2 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SCR-2093</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X35 A2</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>M6X35 A2 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SCR-2094</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X50 A2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>M8X50 A2 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SCR-2095</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X50 A4</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>M10X50 A4 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SCR-2096</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X70 A4</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>M12X70 A4 STAINLESS</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SCR-2097</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M6X25 A2</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>M6X25 A2</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SCR-2098</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M8X30 A2</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>M8X30 A2</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SCR-2099</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X35 A4</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>M10X35 A4</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SCR-2100</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X45 A4</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>M12X45 A4</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SCR-2101</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X40</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>M6X40 8.8</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SCR-2102</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X50</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>M6X50 8.8</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SCR-2103</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X70</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>M8X70 8.8</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SCR-2104</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X80</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>M8X80 8.8</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SCR-2105</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X100</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>M8X100 8.8</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SCR-2106</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X80</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>M10X80 8.8</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SCR-2107</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X90</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>M10X90 8.8</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SCR-2108</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X100</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>M10X100 8.8</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SCR-2109</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X120</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>M12X120 8.8</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SCR-2110</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X140</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>M12X140 8.8</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SCR-2111</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HEX SCREW M14X80</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>M14X80 8.8</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SCR-2112</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HEX SCREW M14X100</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>M14X100 8.8</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SCR-2113</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HEX SCREW M16X140</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>M16X140 8.8</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SCR-2114</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HEX SCREW M16X160 HDG</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>M16X160 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SCR-2115</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HEX SCREW M20X100</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>M20X100 8.8</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SCR-2116</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HEX SCREW M20X140 HDG</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>M20X140 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SCR-2117</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HEX SCREW M24X60</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>M24X60 8.8</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SCR-2118</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HEX SCREW M24X140 HDG</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>M24X140 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SCR-2119</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>HEX SCREW M30X80</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>M30X80 8.8</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SCR-2120</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HEX SCREW M30X140 HDG</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>M30X140 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SCR-2121</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M4X10</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>M4X10 12.9</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SCR-2122</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M4X16</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>M4X16 12.9</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SCR-2123</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M5X12</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>M5X12 10.9</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SCR-2124</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M5X20</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>M5X20 10.9</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SCR-2125</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M6X30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>M6X30 10.9</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SCR-2126</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M6X40</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>M6X40 10.9</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SCR-2127</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M8X35</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>M8X35 10.9</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SCR-2128</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M8X45</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>M8X45 10.9</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SCR-2129</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M8X60</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>M8X60 10.9</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SCR-2130</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X60</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>M10X60 10.9</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SCR-2131</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X70</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>M10X70 10.9</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SCR-2132</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X80</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>M10X80 10.9</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SCR-2133</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X50</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>M12X50 10.9</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SCR-2134</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X60</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>M12X60 10.9</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SCR-2135</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X70</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>M12X70 10.9</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SCR-2136</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M14X60</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>M14X60 10.9</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SCR-2137</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M16X60</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>M16X60 12.9</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SCR-2138</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M16X70</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>M16X70 12.9</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SCR-2139</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M20X70</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>M20X70 10.9</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SCR-2140</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M24X80</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>M24X80 10.9</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SCR-2141</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X30</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>M4X30 8.8</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SCR-2142</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X40</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>M4X40 8.8</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SCR-2143</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X35</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>M5X35 8.8</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SCR-2144</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X40</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>M5X40 8.8</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SCR-2145</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X50</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>M5X50 8.8</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SCR-2146</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X60</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>M6X60 8.8</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SCR-2147</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X70</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>M6X70 8.8</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SCR-2148</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X80</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>M6X80 8.8</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SCR-2149</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X90</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>M8X90 8.8</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SCR-2150</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X110</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>M8X110 8.8</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SCR-2161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>M4X25 8.8</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SCR-2162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HEX SCREW M4X35</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>M4X35 8.8</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SCR-2163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>M5X10 8.8</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SCR-2164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HEX SCREW M5X12</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>M5X12 8.8</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ISO 4017</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SCR-2165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X10</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>M6X10 8.8</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SCR-2166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X12</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>M6X12 8.8</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>ISO 4017</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SCR-2167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X10</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>M8X10 8.8</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SCR-2168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X12</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>M8X12 8.8</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ISO 4017</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SCR-2169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M4X20</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>M4X20 10.9</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SCR-2170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M4X25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>M4X25 10.9</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SCR-2171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M5X25</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>M5X25 10.9</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SCR-2172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M5X30</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>M5X30 10.9</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SCR-2173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M6X20</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>M6X20 10.9</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SCR-2174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M6X50</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>M6X50 10.9</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SCR-2175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M8X20</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>M8X20 10.9</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SCR-2176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X20</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>M10X20 10.9</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SCR-2177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X25</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>M10X25 10.9</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SCR-2178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M10X30</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>M10X30 10.9</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SCR-2179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X30</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>M12X30 10.9</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SCR-2180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M12X80</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>M12X80 10.9</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SCR-2181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M14X50</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>M14X50 10.9</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SCR-2182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M14X70</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>M14X70 10.9</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SCR-2183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M16X80</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>M16X80 10.9</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SCR-2184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M16X100</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>M16X100 10.9</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SCR-2185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SET SCREW M4X6</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>M4X6 45H</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SCR-2186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SET SCREW M4X8</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>M4X8 45H</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SCR-2187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SET SCREW M5X8</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>M5X8 45H</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SCR-2188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SET SCREW M5X10</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>M5X10 45H</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SCR-2189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SET SCREW M6X6</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>M6X6 45H</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SCR-2190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SET SCREW M6X12</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>M6X12 45H</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SCR-2191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SET SCREW M8X16</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>M8X16 45H</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>DIN 913</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SCR-2192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SET SCREW M10X20</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Set screw, flat point</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Kiinnitysruuvi, tasapää</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>M10X20 45H</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>DIN 916</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SCR-2193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M5X16</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>M5X16 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ISO 10642</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SCR-2194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M6X16</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>M6X16 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>DIN 7991</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SCR-2195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M8X20</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>M8X20 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ISO 10642</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SCR-2196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M10X25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>M10X25 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>DIN 7991</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SCR-2197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>COUNTERSUNK SCREW M14X50</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Countersunk head screw</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Upporuuvi</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>M14X50 8.8 COUNTERSUNK</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ISO 10642</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SCR-2198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M4X12</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>M4X12 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SCR-2199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M4X20</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>M4X20 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SCR-2200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M5X12</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>M5X12 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SCR-2201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PAN HEAD SCREW M10X30</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Pan head screw</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Linssiruuvi</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>M10X30 8.8 PAN HEAD</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>DIN 7985</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SCR-2202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M6X16</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>M6X16 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SCR-2203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M8X25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>M8X25 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SCR-2204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M10X30</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>M10X30 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SCR-2205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>FLANGE SCREW M12X35</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Hexagon flange screw</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Laippakantainen ruuvi</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>M12X35 8.8 FLANGE</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>DIN 6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SCR-2206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>HEX SCREW M36X100</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>M36X100 8.8</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SCR-2207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HEX SCREW M36X120 HDG</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>M36X120 8.8 HDG</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SCR-2208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HEX SCREW M42X120</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>M42X120 8.8</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SCR-2209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>HEX SCREW M48X150</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>M48X150 8.8</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SCR-2210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M20X80</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>M20X80 10.9</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SCR-2211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M20X100</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>M20X100 10.9</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ISO 4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SCR-2212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M24X100</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>M24X100 10.9</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SCR-2213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SOCKET HEAD SCREW M30X100</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Hexagon socket head screw</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Kuusiokoloruuvi</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>M30X100 10.9</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SCR-2214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HEX SCREW M6X45</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>M6X45 8.8</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SCR-2215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>HEX SCREW M8X45</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>M8X45 8.8</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SCR-2216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HEX SCREW M10X45</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>M10X45 8.8</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>DIN 933</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SCR-2217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HEX SCREW M12X45</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>M12X45 8.8</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>DIN 931</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SCR-2218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HEX SCREW M14X45</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Hexagon screw</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Kuusioruuvi</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>M14X45 8.8</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ISO 4014</t>
         </is>
       </c>
     </row>
